--- a/docs/設計書/基本設計書.xlsx
+++ b/docs/設計書/基本設計書.xlsx
@@ -1516,7 +1516,7 @@
       <c r="D11" s="6" t="inlineStr"/>
       <c r="E11" s="6" t="inlineStr"/>
       <c r="F11" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="F12" s="14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="94" customHeight="1">
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
